--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,6 +1108,1199 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129025498</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91809</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>658</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>602772</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7021557</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129023473</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91478</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>602700</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7021564</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129025443</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91809</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>602792</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7021544</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129025727</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92210</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>602731</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7021579</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129033780</v>
+      </c>
+      <c r="B10" t="n">
+        <v>45947</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101137</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Reliktslända</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Inocellia crassicornis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schummel, 1832)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gåsnäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>602794</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7021522</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Larv under bark på granlåga</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129033778</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91809</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>658</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gåsnäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>602688</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7021538</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129023691</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98643</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>602699</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7021542</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129023727</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91809</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>658</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>602693</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7021547</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129023710</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91513</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>602692</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7021549</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129023466</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91513</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>602700</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7021564</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129023761</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>602722</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7021521</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129023723</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91809</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>658</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>602692</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7021548</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,45 +1304,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129025727</v>
+        <v>129025443</v>
       </c>
       <c r="B8" t="n">
-        <v>92218</v>
+        <v>91808</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602731</v>
+        <v>602792</v>
       </c>
       <c r="R8" t="n">
-        <v>7021579</v>
+        <v>7021544</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,45 +1401,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129025443</v>
+        <v>129025727</v>
       </c>
       <c r="B9" t="n">
-        <v>91805</v>
+        <v>92223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602792</v>
+        <v>602731</v>
       </c>
       <c r="R9" t="n">
-        <v>7021544</v>
+        <v>7021579</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129023761</v>
+        <v>129023723</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>91808</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,39 +2110,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602722</v>
+        <v>602692</v>
       </c>
       <c r="R16" t="n">
-        <v>7021521</v>
+        <v>7021548</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2175,11 +2170,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2206,10 +2196,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129023723</v>
+        <v>129023761</v>
       </c>
       <c r="B17" t="n">
-        <v>91805</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,34 +2207,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602692</v>
+        <v>602722</v>
       </c>
       <c r="R17" t="n">
-        <v>7021548</v>
+        <v>7021521</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2277,6 +2272,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>129025443</v>
       </c>
       <c r="B8" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>129025727</v>
       </c>
       <c r="B9" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>129023723</v>
       </c>
       <c r="B16" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129023723</v>
+        <v>129023761</v>
       </c>
       <c r="B16" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,34 +2110,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602692</v>
+        <v>602722</v>
       </c>
       <c r="R16" t="n">
-        <v>7021548</v>
+        <v>7021521</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2170,6 +2175,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2196,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129023761</v>
+        <v>129023723</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2207,39 +2217,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602722</v>
+        <v>602692</v>
       </c>
       <c r="R17" t="n">
-        <v>7021521</v>
+        <v>7021548</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2272,11 +2277,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>129025443</v>
       </c>
       <c r="B8" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>129025727</v>
       </c>
       <c r="B9" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129023761</v>
+        <v>129023723</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>91818</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,39 +2110,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602722</v>
+        <v>602692</v>
       </c>
       <c r="R16" t="n">
-        <v>7021521</v>
+        <v>7021548</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2175,11 +2170,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2206,10 +2196,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129023723</v>
+        <v>129023761</v>
       </c>
       <c r="B17" t="n">
-        <v>91811</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,34 +2207,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602692</v>
+        <v>602722</v>
       </c>
       <c r="R17" t="n">
-        <v>7021548</v>
+        <v>7021521</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2277,6 +2272,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,45 +1304,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129025443</v>
+        <v>129025727</v>
       </c>
       <c r="B8" t="n">
-        <v>91818</v>
+        <v>92240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602792</v>
+        <v>602731</v>
       </c>
       <c r="R8" t="n">
-        <v>7021544</v>
+        <v>7021579</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,45 +1401,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129025727</v>
+        <v>129025443</v>
       </c>
       <c r="B9" t="n">
-        <v>92233</v>
+        <v>91825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602731</v>
+        <v>602792</v>
       </c>
       <c r="R9" t="n">
-        <v>7021579</v>
+        <v>7021544</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>129023723</v>
       </c>
       <c r="B16" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>129025727</v>
       </c>
       <c r="B8" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>129025443</v>
       </c>
       <c r="B9" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>129023723</v>
       </c>
       <c r="B16" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>129023761</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1304,45 +1304,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129025727</v>
+        <v>129025443</v>
       </c>
       <c r="B8" t="n">
-        <v>92242</v>
+        <v>91827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602731</v>
+        <v>602792</v>
       </c>
       <c r="R8" t="n">
-        <v>7021579</v>
+        <v>7021544</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,45 +1401,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129025443</v>
+        <v>129025727</v>
       </c>
       <c r="B9" t="n">
-        <v>91827</v>
+        <v>92242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602792</v>
+        <v>602731</v>
       </c>
       <c r="R9" t="n">
-        <v>7021544</v>
+        <v>7021579</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1304,45 +1304,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129025443</v>
+        <v>129025727</v>
       </c>
       <c r="B8" t="n">
-        <v>91827</v>
+        <v>92242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602792</v>
+        <v>602731</v>
       </c>
       <c r="R8" t="n">
-        <v>7021544</v>
+        <v>7021579</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,45 +1401,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129025727</v>
+        <v>129025443</v>
       </c>
       <c r="B9" t="n">
-        <v>92242</v>
+        <v>91827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602731</v>
+        <v>602792</v>
       </c>
       <c r="R9" t="n">
-        <v>7021579</v>
+        <v>7021544</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>129025727</v>
       </c>
       <c r="B8" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>129025443</v>
       </c>
       <c r="B9" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>129023723</v>
       </c>
       <c r="B16" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,45 +1304,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129025727</v>
+        <v>129025443</v>
       </c>
       <c r="B8" t="n">
-        <v>92257</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602731</v>
+        <v>602792</v>
       </c>
       <c r="R8" t="n">
-        <v>7021579</v>
+        <v>7021544</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,45 +1401,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129025443</v>
+        <v>129025727</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>92258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602792</v>
+        <v>602731</v>
       </c>
       <c r="R9" t="n">
-        <v>7021544</v>
+        <v>7021579</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>129023723</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,45 +1304,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129025443</v>
+        <v>129025727</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>92261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602792</v>
+        <v>602731</v>
       </c>
       <c r="R8" t="n">
-        <v>7021544</v>
+        <v>7021579</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,45 +1401,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129025727</v>
+        <v>129025443</v>
       </c>
       <c r="B9" t="n">
-        <v>92258</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602731</v>
+        <v>602792</v>
       </c>
       <c r="R9" t="n">
-        <v>7021579</v>
+        <v>7021544</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129023723</v>
+        <v>129023761</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,34 +2110,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602692</v>
+        <v>602722</v>
       </c>
       <c r="R16" t="n">
-        <v>7021548</v>
+        <v>7021521</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2170,6 +2175,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2196,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129023761</v>
+        <v>129023723</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2207,39 +2217,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602722</v>
+        <v>602692</v>
       </c>
       <c r="R17" t="n">
-        <v>7021521</v>
+        <v>7021548</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2272,11 +2277,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>129025727</v>
       </c>
       <c r="B8" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>129025443</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129023761</v>
+        <v>129023723</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>91843</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,39 +2110,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602722</v>
+        <v>602692</v>
       </c>
       <c r="R16" t="n">
-        <v>7021521</v>
+        <v>7021548</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2175,11 +2170,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2206,10 +2196,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129023723</v>
+        <v>129023761</v>
       </c>
       <c r="B17" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,34 +2207,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602692</v>
+        <v>602722</v>
       </c>
       <c r="R17" t="n">
-        <v>7021548</v>
+        <v>7021521</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2277,6 +2272,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,45 +1304,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129025727</v>
+        <v>129025443</v>
       </c>
       <c r="B8" t="n">
-        <v>92263</v>
+        <v>91847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602731</v>
+        <v>602792</v>
       </c>
       <c r="R8" t="n">
-        <v>7021579</v>
+        <v>7021544</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,45 +1401,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129025443</v>
+        <v>129025727</v>
       </c>
       <c r="B9" t="n">
-        <v>91843</v>
+        <v>92267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602792</v>
+        <v>602731</v>
       </c>
       <c r="R9" t="n">
-        <v>7021544</v>
+        <v>7021579</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>129023723</v>
       </c>
       <c r="B16" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>129025443</v>
       </c>
       <c r="B8" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>129025727</v>
       </c>
       <c r="B9" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>129023723</v>
       </c>
       <c r="B16" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 44441-2025 artfynd.xlsx
+++ b/artfynd/A 44441-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129025498</v>
       </c>
       <c r="B6" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129023473</v>
       </c>
       <c r="B7" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>129025443</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>129025727</v>
       </c>
       <c r="B9" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>129033778</v>
       </c>
       <c r="B11" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>129023691</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>129023727</v>
       </c>
       <c r="B13" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129023710</v>
       </c>
       <c r="B14" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>129023466</v>
       </c>
       <c r="B15" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129023723</v>
+        <v>129023761</v>
       </c>
       <c r="B16" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,34 +2110,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björnberget, Björnberget, Ång</t>
+          <t>Björkbäcken, Björkbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602692</v>
+        <v>602722</v>
       </c>
       <c r="R16" t="n">
-        <v>7021548</v>
+        <v>7021521</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2170,6 +2175,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2196,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129023761</v>
+        <v>129023723</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2207,39 +2217,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkbäcken, Björkbäcken, Ång</t>
+          <t>Björnberget, Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602722</v>
+        <v>602692</v>
       </c>
       <c r="R17" t="n">
-        <v>7021521</v>
+        <v>7021548</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2272,11 +2277,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
